--- a/islem_gecmisi.xlsx
+++ b/islem_gecmisi.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>230</v>
+        <v>384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -588,15 +588,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KRGYO</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2183</v>
+        <v>2134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15.44</t>
+          <t>26.33</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -613,15 +613,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OSTIM</t>
+          <t>TRHOL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7408</v>
+        <v>478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>117.50</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -633,145 +633,145 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>TRHOL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1280</v>
+        <v>478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>26.33</t>
+          <t>105.75</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>STOP</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>DERHL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>286</v>
+        <v>384</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>117.50</t>
+          <t>131.58</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>STOP</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-06-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TRHOL</t>
+          <t>ADESE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>286</v>
+        <v>202350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>105.75</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>ALIS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DERHL</t>
+          <t>KGYO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>230</v>
+        <v>53294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>131.58</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>ALIS</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OSTIM</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7408</v>
+        <v>10962</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>ALIS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KRGYO</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2183</v>
+        <v>10962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>13.90</t>
+          <t>15.14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -783,20 +783,20 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ADESE</t>
+          <t>PEKGY</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>63001</v>
+        <v>22244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>5.34</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -808,20 +808,20 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1490</v>
+        <v>6029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>37.80</t>
+          <t>19.70</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -833,20 +833,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UFUK</t>
+          <t>YAYLA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>59</v>
+        <v>3208</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>950.00</t>
+          <t>37.02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -858,32 +858,32 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GLYHO</t>
+          <t>TEHOL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6529</v>
+        <v>6029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8.47</t>
+          <t>17.73</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>STOP</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -892,11 +892,11 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5118</v>
+        <v>21438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>19.04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -908,20 +908,20 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>KGYO</t>
+          <t>CRDFA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15975</v>
+        <v>11003</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>28.20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -933,20 +933,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SNGYO</t>
+          <t>ECZYT</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12562</v>
+        <v>972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4.40</t>
+          <t>319.00</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -958,20 +958,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>HEDEF</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3286</v>
+        <v>4859</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>63.85</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -983,95 +983,95 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TEHOL</t>
+          <t>POLHO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3286</v>
+        <v>14142</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>21.94</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>ALIS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DAPGM</t>
+          <t>POLHO</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4177</v>
+        <v>14142</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13.38</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>STOP</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EMKEL</t>
+          <t>ECZYT</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>697</v>
+        <v>972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>80.10</t>
+          <t>287.10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>STOP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PEKGY</t>
+          <t>CEMZY</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>10468</v>
+        <v>3177</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1083,20 +1083,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>HDFGS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>591</v>
+        <v>31000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>94.50</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1108,20 +1108,20 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>YAYLA</t>
+          <t>HUBVC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1510</v>
+        <v>45163</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>37.02</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1133,45 +1133,45 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EMKEL</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>697</v>
+        <v>35097</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>ALIS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EYGYO</t>
+          <t>LYDHO</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26041</v>
+        <v>832</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>213.70</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1183,20 +1183,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GIPTA</t>
+          <t>MAGEN</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>789</v>
+        <v>6187</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>151.20</t>
+          <t>28.76</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1208,20 +1208,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>ONCSM</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>6270</v>
+        <v>862</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>19.04</t>
+          <t>206.30</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1233,45 +1233,45 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GIPTA</t>
+          <t>UFUK</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>789</v>
+        <v>82</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>136.08</t>
+          <t>2170.00</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>ALIS</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EYGYO</t>
+          <t>CEMZY</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>26041</v>
+        <v>3177</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>50.40</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1283,145 +1283,145 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AVOD</t>
+          <t>HDFGS</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>17353</v>
+        <v>31000</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>STOP</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CRDFA</t>
+          <t>LYDHO</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2923</v>
+        <v>832</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>28.20</t>
+          <t>192.33</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>STOP</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ECZYT</t>
+          <t>UFUK</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>258</v>
+        <v>82</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>319.00</t>
+          <t>1953.00</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>STOP</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>HUBVC</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1291</v>
+        <v>45163</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>63.85</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>STOP</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>INFO</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2679</v>
+        <v>35097</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>STOP</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>POLHO</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3757</v>
+        <v>7602</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>21.94</t>
+          <t>180.00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1433,20 +1433,20 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>YGGYO</t>
+          <t>COSMO</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>584</v>
+        <v>7266</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>141.00</t>
+          <t>263.00</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1458,20 +1458,20 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AVOD</t>
+          <t>COSMO</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>17353</v>
+        <v>7266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>236.70</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1483,823 +1483,173 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>POLHO</t>
+          <t>ALKLC</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3757</v>
+        <v>1600</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>267.50</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>ALIS</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>YGGYO</t>
+          <t>CVKMD</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>584</v>
+        <v>10834</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>126.90</t>
+          <t>39.52</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>ALIS</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ECZYT</t>
+          <t>ENKAI</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>258</v>
+        <v>4535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>287.10</t>
+          <t>94.40</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>ALIS</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IEYHO</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2679</v>
+        <v>761</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>27.68</t>
+          <t>562.50</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>ALIS</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CEMZY</t>
+          <t>KLRHO</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1190</v>
+        <v>761</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>56.00</t>
+          <t>506.25</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>STOP</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HDFGS</t>
+          <t>CVKMD</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>11610</v>
+        <v>10834</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>35.57</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ALIS</t>
+          <t>STOP</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HUBVC</t>
+          <t>GUNDG</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>16915</v>
+        <v>3155</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>532.00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>13145</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>5.07</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>LYDHO</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>311</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>213.70</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>MAGEN</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>2317</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>28.76</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>METRO</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>10446</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>6.38</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>ONCSM</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>323</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>206.30</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>TDGYO</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>2302</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>28.94</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>CEMZY</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>1190</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>50.40</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>STOP</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>HDFGS</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>11610</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>5.17</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>STOP</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>LYDHO</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>311</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>192.33</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>STOP</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>HUBVC</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>16915</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>STOP</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>13145</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>4.56</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>STOP</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>METRO</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>10446</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>5.74</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>STOP</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>GUNDG</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>3245</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>180.00</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>COSMO</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1550</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>263.00</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>TCKRC</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>6725</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>60.65</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-01-30</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>COSMO</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>1550</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>236.70</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>STOP</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>ALKLC</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>734</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>267.50</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>CVKMD</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>4971</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>39.52</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>ENKAI</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>2081</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>94.40</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>KLRHO</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>349</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>562.50</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>2026-02-01</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>LIDFA</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>62366</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>KLRHO</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>349</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>506.25</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>STOP</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>2026-02-19</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>CVKMD</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>4971</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>35.57</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>STOP</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>EDATA</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>25888</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>12.42</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>GUNDG</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>604</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>532.00</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>ALIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>ODINE</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>557</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>576.50</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
         <is>
           <t>ALIS</t>
         </is>
